--- a/Mantenimiento/excels/LA_LIBERTAD-TRUJILLO-TRUJILLO.xlsx
+++ b/Mantenimiento/excels/LA_LIBERTAD-TRUJILLO-TRUJILLO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,11 +484,6 @@
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>mantenimiento</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -498,7 +493,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -536,11 +531,6 @@
       <c r="K2" t="n">
         <v>0</v>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -550,7 +540,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -588,11 +578,6 @@
       <c r="K3" t="n">
         <v>0</v>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -602,7 +587,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -640,11 +625,6 @@
       <c r="K4" t="n">
         <v>0</v>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -654,7 +634,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,11 +672,6 @@
       <c r="K5" t="n">
         <v>0</v>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -706,7 +681,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -744,11 +719,6 @@
       <c r="K6" t="n">
         <v>0</v>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -758,7 +728,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -796,11 +766,6 @@
       <c r="K7" t="n">
         <v>0</v>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -810,7 +775,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -848,11 +813,6 @@
       <c r="K8" t="n">
         <v>0</v>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -862,7 +822,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -900,11 +860,6 @@
       <c r="K9" t="n">
         <v>0</v>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -914,7 +869,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -952,11 +907,6 @@
       <c r="K10" t="n">
         <v>1</v>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -966,7 +916,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1003,11 +953,6 @@
       </c>
       <c r="K11" t="n">
         <v>0</v>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/Mantenimiento/excels/LA_LIBERTAD-TRUJILLO-TRUJILLO.xlsx
+++ b/Mantenimiento/excels/LA_LIBERTAD-TRUJILLO-TRUJILLO.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,61 +413,61 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
@@ -516,20 +504,30 @@
           <t>80003 ANDRES AVELINO CACERES</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-8.11725</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-79.02449</v>
-      </c>
-      <c r="I2" t="n">
-        <v>337</v>
-      </c>
-      <c r="J2" t="n">
-        <v>15</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-8.11725</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-79.02449</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>337</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -563,20 +561,30 @@
           <t>80014 JUAN PABLO II</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-8.108176</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-79.04526</v>
-      </c>
-      <c r="I3" t="n">
-        <v>496</v>
-      </c>
-      <c r="J3" t="n">
-        <v>20</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-8.108176</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-79.04526</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>496</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -610,20 +618,30 @@
           <t>81653 NUESTRA SEÑORA DE MONTSERRAT</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-8.123239999999999</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-79.03234999999999</v>
-      </c>
-      <c r="I4" t="n">
-        <v>339</v>
-      </c>
-      <c r="J4" t="n">
-        <v>14</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-8.12324</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-79.03235</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>339</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -649,28 +667,38 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>250819</t>
+          <t>252106</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>INGENIERIA</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>-8.121560000000002</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-79.03677999999999</v>
-      </c>
-      <c r="I5" t="n">
-        <v>656</v>
-      </c>
-      <c r="J5" t="n">
-        <v>38</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+          <t>SAGRADO CORAZON</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-8.0954</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-79.01109</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>748</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -696,28 +724,38 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>252106</t>
+          <t>255732</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>SAGRADO CORAZON</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>-8.0954</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-79.01109</v>
-      </c>
-      <c r="I6" t="n">
-        <v>748</v>
-      </c>
-      <c r="J6" t="n">
-        <v>37</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+          <t>CLARETIANO</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-8.12918</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-79.03632</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1235</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -743,28 +781,38 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>255732</t>
+          <t>540353</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CLARETIANO</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>-8.12918</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-79.03632</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1235</v>
-      </c>
-      <c r="J7" t="n">
-        <v>82</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+          <t>HANS HEINRICH BRUNING</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-8.12683</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-79.02998</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>564</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -790,28 +838,38 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>540353</t>
+          <t>657338</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>HANS HEINRICH BRUNING</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>-8.12683</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-79.02997999999999</v>
-      </c>
-      <c r="I8" t="n">
-        <v>564</v>
-      </c>
-      <c r="J8" t="n">
-        <v>33</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+          <t>INTEGRAL CLASS</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-8.11736</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-79.03386</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>447</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -837,122 +895,38 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>657338</t>
+          <t>744251</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>INTEGRAL CLASS</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>-8.11736</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-79.03386</v>
-      </c>
-      <c r="I9" t="n">
-        <v>447</v>
-      </c>
-      <c r="J9" t="n">
-        <v>27</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>130101</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>716875</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>EL CULTURAL AMERICAN SCHOOL</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>-8.11726</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-79.03255</v>
-      </c>
-      <c r="I10" t="n">
-        <v>539</v>
-      </c>
-      <c r="J10" t="n">
-        <v>40</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>130101</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>744251</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
           <t>81014 PEDRO MERCEDES UREÑA</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-8.11221643601271</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-79.04872753899031</v>
-      </c>
-      <c r="I11" t="n">
-        <v>2363</v>
-      </c>
-      <c r="J11" t="n">
-        <v>92</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-8.11221643601271</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-79.0487275389903</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2363</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
   </sheetData>
